--- a/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
+++ b/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>1200 mm</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -230,7 +230,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát hạt mịn đến hạt vừa màu xám ghi, xám vàng, khi chỗ kẹp sét pha, kết cấu chặt vừa đến chặt</t>
+    <t>Cát mịn đến hạt vừa, màu xám ghi, xám vàng, khi chỗ kẹp sét pha, kết cấu chặt vừa đến chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15h13
@@ -321,7 +321,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát mịn đến vừa, màu xám nâu, xám ghi, đôi chỗ lẫn sạn, kết cấu rất chặt</t>
+    <t>Cát mịn đến hạt vừa, màu xám nâu, xám ghi, đôi chỗ lẫn sạn, kết cấu rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10h50

--- a/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
+++ b/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="106">
   <si>
     <t>Dự án</t>
   </si>
@@ -38,10 +38,10 @@
     <t>TP-01 (T29)</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>01/VHGP/SGC/VAP</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Cát san lấp, Cát mịn lẫn bụi, lẫn vỏ sò, màu xám nâu, màu xám ghi, kết cấu xốp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">14h50
@@ -140,7 +140,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha - sét pha màu xám ghi, xám xanh, đôi khi lẫn vỏ sò, hữu cơ, trạng thái dẻo mềm đến dẻo chảy</t>
+    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo mềm, dẻo chảy đến chảy</t>
   </si>
   <si>
     <t xml:space="preserve">10h23
@@ -164,7 +164,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét pha màu xám ghi, xám vàng, trạng thái dẻo cứng đến nửa cứng</t>
+    <t>Sét pha, xám xanh, xám đen, xám ghi, xám vàng, nâu đỏ, TT dẻo cứng đến nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">12h20
@@ -230,7 +230,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát mịn đến hạt vừa, màu xám ghi, xám vàng, khi chỗ kẹp sét pha, kết cấu chặt vừa đến chặt</t>
+    <t>Cát mịn đến hạt vừa, màu xám ghi, xám vàng, đôi chỗ kẹp sét pha, kết cấu chặt vừa đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15h13
@@ -321,9 +321,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát mịn đến hạt vừa, màu xám nâu, xám ghi, đôi chỗ lẫn sạn, kết cấu rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">10h50
 09/03/2026</t>
   </si>
@@ -366,16 +363,13 @@
   </si>
   <si>
     <t>TỔNG CỘNG</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -426,11 +420,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF4C1D95"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
@@ -449,7 +438,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -499,11 +488,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -604,7 +588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -663,22 +647,13 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2158,89 +2133,89 @@
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D37" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="F37" s="19">
+      <c r="F37" s="16">
         <v>-49.41</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="16">
         <v>-50.1</v>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="16">
         <v>0.02</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="16">
         <v>0.69</v>
       </c>
       <c r="J37" s="8">
         <v>41.4</v>
       </c>
-      <c r="K37" s="20" t="s">
+      <c r="K37" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E38" s="21" t="s">
+      <c r="F38" s="16">
+        <v>-50.1</v>
+      </c>
+      <c r="G38" s="16">
+        <v>-52</v>
+      </c>
+      <c r="H38" s="16">
+        <v>2.58</v>
+      </c>
+      <c r="I38" s="16">
+        <v>1.9</v>
+      </c>
+      <c r="J38" s="19">
+        <v>0.74</v>
+      </c>
+      <c r="K38" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="F38" s="19">
-        <v>-50.1</v>
-      </c>
-      <c r="G38" s="19">
-        <v>-52</v>
-      </c>
-      <c r="H38" s="19">
-        <v>2.58</v>
-      </c>
-      <c r="I38" s="19">
-        <v>1.9</v>
-      </c>
-      <c r="J38" s="22">
-        <v>0.74</v>
-      </c>
-      <c r="K38" s="20" t="s">
+    </row>
+    <row r="41" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="41" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="23"/>
-      <c r="K41" s="23"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
     </row>
     <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2322,7 +2297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2335,31 +2310,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2460,79 +2435,50 @@
         <v>66</v>
       </c>
       <c r="D5" s="16">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" s="16">
         <v>-27.44</v>
       </c>
       <c r="F5" s="16">
-        <v>-49.41</v>
+        <v>-52</v>
       </c>
       <c r="G5" s="16">
-        <v>3.87</v>
+        <v>6.47</v>
       </c>
       <c r="H5" s="16">
-        <v>21.97</v>
-      </c>
-      <c r="I5" s="8">
-        <v>5.68</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" s="19">
-        <v>2</v>
-      </c>
-      <c r="E6" s="19">
-        <v>-49.41</v>
-      </c>
-      <c r="F6" s="19">
+        <v>24.56</v>
+      </c>
+      <c r="I5" s="9">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="22">
+        <v>28</v>
+      </c>
+      <c r="E6" s="22">
+        <v>2.6</v>
+      </c>
+      <c r="F6" s="22">
         <v>-52</v>
       </c>
-      <c r="G6" s="19">
-        <v>2.6</v>
-      </c>
-      <c r="H6" s="19">
-        <v>2.59</v>
+      <c r="G6" s="22">
+        <v>12.45</v>
+      </c>
+      <c r="H6" s="22">
+        <v>54.6</v>
       </c>
       <c r="I6" s="22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="25">
-        <v>28</v>
-      </c>
-      <c r="E7" s="25">
-        <v>2.6</v>
-      </c>
-      <c r="F7" s="25">
-        <v>-52</v>
-      </c>
-      <c r="G7" s="25">
-        <v>12.45</v>
-      </c>
-      <c r="H7" s="25">
-        <v>54.6</v>
-      </c>
-      <c r="I7" s="25">
         <v>4.39</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
+++ b/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="107">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Khu đô thị du lịch lấn biển Cần Giờ</t>
+    <t>Cần Giờ</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0002</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>TỔNG CỘNG</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -2458,10 +2461,10 @@
         <v>105</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="D6" s="22">
         <v>28</v>

--- a/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
+++ b/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi</t>
+    <t>Cáp treo - khu VAP</t>
   </si>
   <si>
     <t>Tên bộ phận</t>

--- a/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
+++ b/SGC-CKN/Excel/21dfaf7c-7479-49e3-8ca1-62d521cf5517_Cọc_khoan_nhồi_TP-01__T29__TP-01__T29__1200_mm_09-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TP-01 (T29)</t>
+    <t>19</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -140,7 +140,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo mềm, dẻo chảy đến chảy</t>
+    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo chảy đến chảy</t>
   </si>
   <si>
     <t xml:space="preserve">10h23
